--- a/data/trans_camb/IP2001-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP2001-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 4,69</t>
+          <t>-11,87; 5,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 13,91</t>
+          <t>-6,9; 14,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,93; -9,86</t>
+          <t>-22,14; -9,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 10,75</t>
+          <t>-8,41; 10,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 8,18</t>
+          <t>-10,5; 9,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,85; -1,38</t>
+          <t>-19,6; -2,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 5,16</t>
+          <t>-7,54; 5,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 8,16</t>
+          <t>-6,09; 8,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-18,4; -7,43</t>
+          <t>-17,85; -7,03</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-58,57; 50,72</t>
+          <t>-59,55; 60,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,05; 132,66</t>
+          <t>-37,82; 129,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-38,21; 102,4</t>
+          <t>-42,6; 94,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,86; 65,24</t>
+          <t>-53,42; 83,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-93,14; 2,94</t>
+          <t>-92,21; 14,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 40,26</t>
+          <t>-40,02; 44,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,97; 60,09</t>
+          <t>-35,06; 70,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-95,63; -50,41</t>
+          <t>-95,5; -44,71</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 5,46</t>
+          <t>-1,63; 5,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 5,78</t>
+          <t>-0,81; 5,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,02; -1,37</t>
+          <t>-7,13; -1,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 5,89</t>
+          <t>-0,33; 5,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 6,04</t>
+          <t>-0,08; 6,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 1,28</t>
+          <t>-4,18; 1,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 4,7</t>
+          <t>0,14; 4,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,87</t>
+          <t>0,49; 4,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,75; -0,8</t>
+          <t>-4,71; -0,57</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 71,33</t>
+          <t>-15,92; 71,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 80,88</t>
+          <t>-8,1; 77,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-66,78; -17,92</t>
+          <t>-66,53; -17,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 106,43</t>
+          <t>-4,23; 101,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 104,63</t>
+          <t>-1,61; 107,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,02; 22,03</t>
+          <t>-51,1; 26,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 68,39</t>
+          <t>1,69; 69,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 69,59</t>
+          <t>5,27; 69,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-53,4; -11,45</t>
+          <t>-51,7; -7,79</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 3,94</t>
+          <t>-3,1; 3,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 6,36</t>
+          <t>-1,3; 6,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 5,34</t>
+          <t>-2,4; 5,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 2,45</t>
+          <t>-6,63; 2,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 5,26</t>
+          <t>-4,29; 5,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 5,34</t>
+          <t>-4,23; 5,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 2,1</t>
+          <t>-3,58; 1,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 4,68</t>
+          <t>-1,59; 4,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 4,74</t>
+          <t>-1,91; 4,39</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-64,99; 203,6</t>
+          <t>-60,64; 208,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,69; 336,33</t>
+          <t>-29,07; 333,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,33; 281,11</t>
+          <t>-49,39; 244,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-74,3; 62,42</t>
+          <t>-73,4; 66,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-45,57; 114,38</t>
+          <t>-49,79; 117,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-47,76; 118,29</t>
+          <t>-46,98; 129,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,51; 61,0</t>
+          <t>-55,57; 58,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,19; 128,25</t>
+          <t>-24,73; 115,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-27,92; 123,55</t>
+          <t>-32,59; 111,09</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,33</t>
+          <t>-1,45; 3,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 4,59</t>
+          <t>-0,72; 4,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,37; -2,03</t>
+          <t>-6,27; -1,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,93</t>
+          <t>-1,1; 4,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 4,22</t>
+          <t>-0,84; 4,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 0,37</t>
+          <t>-4,48; 0,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 3,04</t>
+          <t>-0,53; 3,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 3,69</t>
+          <t>0,13; 3,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,39; -1,33</t>
+          <t>-4,6; -1,34</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 45,07</t>
+          <t>-15,29; 50,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 62,88</t>
+          <t>-8,4; 61,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-65,01; -25,35</t>
+          <t>-64,07; -22,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 58,66</t>
+          <t>-12,22; 58,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 61,25</t>
+          <t>-9,81; 62,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-47,91; 6,18</t>
+          <t>-47,49; 6,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 41,72</t>
+          <t>-6,0; 43,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 48,96</t>
+          <t>1,51; 51,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-49,18; -17,38</t>
+          <t>-50,63; -17,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2001-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP2001-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 5,34</t>
+          <t>-11,76; 4,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 14,27</t>
+          <t>-7,19; 13,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,14; -9,4</t>
+          <t>-22,07; -9,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 10,6</t>
+          <t>-9,16; 11,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 9,62</t>
+          <t>-9,95; 8,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,6; -2,07</t>
+          <t>-18,4; -1,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 5,11</t>
+          <t>-7,81; 4,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 8,42</t>
+          <t>-6,3; 7,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,85; -7,03</t>
+          <t>-18,0; -7,48</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-59,55; 60,09</t>
+          <t>-58,29; 40,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,82; 129,72</t>
+          <t>-38,18; 136,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,6; 94,61</t>
+          <t>-43,94; 100,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,42; 83,61</t>
+          <t>-48,61; 86,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-92,21; 14,08</t>
+          <t>-91,67; -1,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,02; 44,53</t>
+          <t>-42,56; 40,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,06; 70,72</t>
+          <t>-34,55; 60,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-95,5; -44,71</t>
+          <t>-95,18; -48,53</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 5,27</t>
+          <t>-1,62; 5,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 5,71</t>
+          <t>-1,27; 5,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,13; -1,6</t>
+          <t>-7,19; -1,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 5,62</t>
+          <t>-0,32; 5,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 6,1</t>
+          <t>0,02; 5,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 1,38</t>
+          <t>-4,01; 1,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 4,85</t>
+          <t>0,01; 4,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,84</t>
+          <t>0,14; 4,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,71; -0,57</t>
+          <t>-4,68; -0,77</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 71,8</t>
+          <t>-15,4; 73,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 77,76</t>
+          <t>-11,5; 76,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-66,53; -17,36</t>
+          <t>-66,67; -20,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 101,78</t>
+          <t>-4,43; 96,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 107,54</t>
+          <t>-0,39; 106,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,1; 26,2</t>
+          <t>-49,49; 23,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 69,57</t>
+          <t>0,11; 62,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,27; 69,0</t>
+          <t>1,44; 74,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-51,7; -7,79</t>
+          <t>-52,49; -11,04</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 3,74</t>
+          <t>-3,03; 3,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 6,45</t>
+          <t>-1,17; 6,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 5,16</t>
+          <t>-2,39; 4,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 2,6</t>
+          <t>-6,67; 2,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 5,09</t>
+          <t>-4,24; 5,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 5,95</t>
+          <t>-4,04; 5,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 1,92</t>
+          <t>-3,59; 2,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 4,49</t>
+          <t>-1,7; 4,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 4,39</t>
+          <t>-1,71; 4,61</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-60,64; 208,73</t>
+          <t>-60,42; 209,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,07; 333,07</t>
+          <t>-27,37; 312,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-49,39; 244,37</t>
+          <t>-50,77; 233,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-73,4; 66,94</t>
+          <t>-71,68; 63,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-49,79; 117,24</t>
+          <t>-48,67; 121,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-46,98; 129,84</t>
+          <t>-45,82; 125,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,57; 58,21</t>
+          <t>-54,06; 58,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,73; 115,72</t>
+          <t>-25,53; 120,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,59; 111,09</t>
+          <t>-28,02; 128,2</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,56</t>
+          <t>-1,73; 3,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,6</t>
+          <t>-0,39; 4,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,27; -1,68</t>
+          <t>-6,39; -2,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 4,01</t>
+          <t>-1,15; 3,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 4,41</t>
+          <t>-0,84; 4,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 0,29</t>
+          <t>-4,64; 0,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 3,2</t>
+          <t>-0,62; 3,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 3,71</t>
+          <t>-0,03; 3,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,6; -1,34</t>
+          <t>-4,51; -1,37</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 50,27</t>
+          <t>-18,44; 51,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 61,07</t>
+          <t>-5,29; 65,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-64,07; -22,47</t>
+          <t>-64,96; -27,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 58,14</t>
+          <t>-12,31; 57,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 62,37</t>
+          <t>-9,06; 60,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-47,49; 6,69</t>
+          <t>-49,63; 5,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 43,66</t>
+          <t>-6,93; 40,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,51; 51,26</t>
+          <t>-0,49; 46,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-50,63; -17,93</t>
+          <t>-50,67; -18,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2001-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP2001-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,08</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,22</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-10,51</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-3,32</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3,24</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-15,11</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,08</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,22</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-10,89</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>-1,19</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-12,85</t>
+          <t>-12,56</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 4,29</t>
+          <t>-7,64; 10,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 13,82</t>
+          <t>-11,67; 8,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,07; -9,58</t>
+          <t>-18,37; -0,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 11,36</t>
+          <t>-11,69; 4,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 8,76</t>
+          <t>-6,71; 13,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,4; -1,68</t>
+          <t>-21,93; -9,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 4,86</t>
+          <t>-7,8; 5,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 7,58</t>
+          <t>-5,77; 8,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-18,0; -7,48</t>
+          <t>-18,13; -6,76</t>
         </is>
       </c>
     </row>
@@ -730,34 +730,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-7,68%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-66,38%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-21,96%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>21,43%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-7,68%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-68,77%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>-7,69%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-83,15%</t>
+          <t>-81,24%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-58,29; 40,59</t>
+          <t>-38,21; 102,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,18; 136,81</t>
+          <t>-55,86; 65,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>-92,34; 11,6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-58,57; 50,72</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>-37,05; 132,66</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-43,94; 100,66</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-48,61; 86,64</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-91,67; -1,99</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,56; 40,55</t>
+          <t>-41,36; 40,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 60,28</t>
+          <t>-30,97; 60,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-95,18; -48,53</t>
+          <t>-95,05; -41,49</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,74</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,91</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-1,3</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,89</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,19</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,23</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,74</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,91</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,41</t>
+          <t>-3,86</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,73</t>
+          <t>-2,5</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 5,37</t>
+          <t>-0,42; 5,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 5,33</t>
+          <t>-0,41; 6,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,19; -1,56</t>
+          <t>-4,07; 1,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 5,61</t>
+          <t>-1,29; 5,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 5,9</t>
+          <t>-1,1; 5,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,25</t>
+          <t>-6,65; -0,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 4,26</t>
+          <t>0,17; 4,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 4,91</t>
+          <t>0,34; 4,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; -0,77</t>
+          <t>-4,48; -0,56</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>39,28%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>41,74%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-18,71%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>21,14%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>24,47%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-47,36%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>39,28%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>41,74%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-20,25%</t>
+          <t>-43,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-34,65%</t>
+          <t>-31,74%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 73,06</t>
+          <t>-4,76; 106,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 76,76</t>
+          <t>-6,55; 104,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-66,67; -20,62</t>
+          <t>-49,6; 25,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 96,63</t>
+          <t>-13,51; 71,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 106,82</t>
+          <t>-10,5; 80,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,49; 23,5</t>
+          <t>-63,45; -11,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 62,79</t>
+          <t>1,55; 68,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 74,45</t>
+          <t>3,57; 69,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-52,49; -11,04</t>
+          <t>-50,24; -7,37</t>
         </is>
       </c>
     </row>
@@ -1056,47 +1056,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,08</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,28</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,44</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,06</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-0,9</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1,56</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>1,25</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,23</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,76</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-0,9</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,56</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 3,95</t>
+          <t>-6,87; 2,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 6,5</t>
+          <t>-4,36; 5,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 4,77</t>
+          <t>-4,13; 5,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 2,0</t>
+          <t>-3,25; 3,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 5,41</t>
+          <t>-1,15; 6,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 5,85</t>
+          <t>-2,31; 4,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 2,08</t>
+          <t>-3,5; 2,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 4,39</t>
+          <t>-1,77; 4,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 4,61</t>
+          <t>-1,69; 4,87</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-32,79%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15,88%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>7,65%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>67,15%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>34,24%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-32,79%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-60,42; 209,16</t>
+          <t>-74,3; 62,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,37; 312,69</t>
+          <t>-45,57; 114,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-50,77; 233,35</t>
+          <t>-45,98; 129,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-71,68; 63,43</t>
+          <t>-64,99; 203,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,67; 121,44</t>
+          <t>-29,69; 336,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,82; 125,82</t>
+          <t>-48,75; 264,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-54,06; 58,28</t>
+          <t>-55,51; 61,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-25,53; 120,11</t>
+          <t>-27,19; 128,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-28,02; 128,2</t>
+          <t>-28,24; 122,98</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,43</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,72</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,81</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,89</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,06</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,08</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,43</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,72</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,99</t>
+          <t>-3,83</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,98</t>
+          <t>-2,77</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 3,68</t>
+          <t>-0,79; 3,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 4,77</t>
+          <t>-0,8; 4,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,39; -2,0</t>
+          <t>-4,25; 0,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,99</t>
+          <t>-1,54; 3,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 4,18</t>
+          <t>-0,77; 4,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 0,31</t>
+          <t>-6,13; -1,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,01</t>
+          <t>-0,57; 3,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 3,47</t>
+          <t>-0,05; 3,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,51; -1,37</t>
+          <t>-4,29; -1,13</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>17,87%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>21,54%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-22,66%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>10,52%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>24,4%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-48,38%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>17,87%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>21,54%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-24,92%</t>
+          <t>-45,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-36,26%</t>
+          <t>-33,79%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 51,43</t>
+          <t>-8,92; 58,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 65,8</t>
+          <t>-9,0; 61,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-64,96; -27,08</t>
+          <t>-45,82; 10,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 57,33</t>
+          <t>-16,21; 45,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 60,32</t>
+          <t>-7,86; 62,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,63; 5,38</t>
+          <t>-63,21; -22,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 40,15</t>
+          <t>-6,41; 41,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 46,89</t>
+          <t>-0,77; 48,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-50,67; -18,65</t>
+          <t>-47,2; -14,23</t>
         </is>
       </c>
     </row>
